--- a/R/quick-start/MyResults.xlsx
+++ b/R/quick-start/MyResults.xlsx
@@ -22,7 +22,7 @@
     <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Apr/29/2021</t>
+    <t xml:space="preserve">Jun/15/2021</t>
   </si>
   <si>
     <t xml:space="preserve">Output file</t>
